--- a/1-运维服务目录/JXTX-01-02-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/JXTX-01-02-组织级运维服务目录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575" tabRatio="751"/>
+    <workbookView windowWidth="23040" windowHeight="9060" tabRatio="751" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="修订页" sheetId="68" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="142">
   <si>
     <t>江西通信产业服务有限公司</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>服务内容概要说明</t>
+  </si>
+  <si>
+    <t>04</t>
   </si>
   <si>
     <t>0403</t>
@@ -1399,16 +1402,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -2858,48 +2861,48 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="3"/>
     </row>
     <row r="2" ht="17.25" customHeight="1" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:2">
@@ -2907,79 +2910,79 @@
         <v>28</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" ht="32.25" customHeight="1" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" ht="144.75" customHeight="1" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3057,12 +3060,14 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="27"/>
+      <c r="A3" s="27" t="s">
+        <v>30</v>
+      </c>
       <c r="B3" s="28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="30"/>
       <c r="E3" s="31"/>
@@ -3077,10 +3082,10 @@
       <c r="B4" s="28"/>
       <c r="C4" s="35"/>
       <c r="D4" s="36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="30"/>
       <c r="G4" s="32"/>
@@ -3095,10 +3100,10 @@
       <c r="D5" s="30"/>
       <c r="E5" s="5"/>
       <c r="F5" s="36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" s="32"/>
       <c r="I5" s="33"/>
@@ -3113,13 +3118,13 @@
       <c r="F6" s="30"/>
       <c r="G6" s="38"/>
       <c r="H6" s="39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" s="40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:10">
@@ -3131,13 +3136,13 @@
       <c r="F7" s="30"/>
       <c r="G7" s="38"/>
       <c r="H7" s="39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I7" s="40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J7" s="40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1" spans="1:10">
@@ -3149,13 +3154,13 @@
       <c r="F8" s="42"/>
       <c r="G8" s="43"/>
       <c r="H8" s="39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I8" s="40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1" spans="1:10">
@@ -3167,13 +3172,13 @@
       <c r="F9" s="30"/>
       <c r="G9" s="38"/>
       <c r="H9" s="39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="30.9" customHeight="1" spans="1:10">
@@ -3181,10 +3186,10 @@
       <c r="B10" s="28"/>
       <c r="C10" s="35"/>
       <c r="D10" s="36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10" s="44"/>
       <c r="G10" s="32"/>
@@ -3199,10 +3204,10 @@
       <c r="D11" s="30"/>
       <c r="E11" s="5"/>
       <c r="F11" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="45" t="s">
         <v>50</v>
-      </c>
-      <c r="G11" s="45" t="s">
-        <v>49</v>
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="33"/>
@@ -3217,13 +3222,13 @@
       <c r="F12" s="46"/>
       <c r="G12" s="38"/>
       <c r="H12" s="47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J12" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="32.1" customHeight="1" spans="1:10">
@@ -3235,13 +3240,13 @@
       <c r="F13" s="46"/>
       <c r="G13" s="38"/>
       <c r="H13" s="47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I13" s="40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J13" s="40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="39" customHeight="1" spans="1:10">
@@ -3253,13 +3258,13 @@
       <c r="F14" s="46"/>
       <c r="G14" s="38"/>
       <c r="H14" s="39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J14" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:10">
@@ -3271,13 +3276,13 @@
       <c r="F15" s="46"/>
       <c r="G15" s="38"/>
       <c r="H15" s="47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3313,126 +3318,126 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" ht="21" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" ht="288" spans="1:2">
       <c r="A12" s="21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3459,126 +3464,126 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" ht="178.2" customHeight="1" spans="1:2">
       <c r="A12" s="21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3605,126 +3610,126 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" ht="230.4" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3751,48 +3756,48 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B1" s="3"/>
     </row>
     <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="62" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:2">
@@ -3800,79 +3805,79 @@
         <v>28</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="42.75" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="120.75" customHeight="1" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3898,126 +3903,126 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="63" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="3"/>
     </row>
     <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="36.75" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:2">
       <c r="A10" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="13"/>
     </row>
     <row r="11" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" ht="259.2" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4044,126 +4049,126 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="63" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B1" s="3"/>
     </row>
     <row r="2" ht="24.75" customHeight="1" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" ht="24.75" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" ht="24.75" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" ht="24.75" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" ht="24.75" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" ht="24.75" customHeight="1" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="24.75" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" ht="33.75" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" s="13"/>
     </row>
     <row r="11" ht="15.6" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" ht="226.2" customHeight="1" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -4190,48 +4195,48 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:2">
       <c r="A7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:2">
@@ -4239,79 +4244,79 @@
         <v>28</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" ht="28.8" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:2">
       <c r="A12" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="222.6" customHeight="1" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1" spans="1:2">
       <c r="A16" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1" spans="1:2">
       <c r="A17" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/1-运维服务目录/JXTX-01-02-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/JXTX-01-02-组织级运维服务目录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" tabRatio="751" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="23040" windowHeight="9060" tabRatio="751" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="修订页" sheetId="68" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="针对质监行业领域的应用软件优化改善服务">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">修订页!$A$5:$H$14</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +41,7 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>微软用户</author>
@@ -54,6 +54,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t>微软用户:</t>
@@ -62,6 +63,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -263,6 +265,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>040303010</t>
@@ -271,6 +274,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>4</t>
@@ -288,6 +292,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>040301010</t>
@@ -297,6 +302,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -306,6 +312,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>数据库系统巡检服务</t>
@@ -417,6 +424,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>040301010</t>
@@ -426,6 +434,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -435,6 +444,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>数据库系统故障处理服务</t>
@@ -479,6 +489,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -490,6 +501,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -500,6 +512,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -510,6 +523,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -521,6 +535,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -531,6 +546,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -542,6 +558,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -552,6 +569,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -563,6 +581,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -573,6 +592,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -584,6 +604,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -594,6 +615,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -605,6 +627,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -615,6 +638,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -625,6 +649,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -636,6 +661,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -646,6 +672,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -657,6 +684,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -667,6 +695,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -677,6 +706,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -687,6 +717,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -698,6 +729,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -708,6 +740,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -719,6 +752,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -729,6 +763,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -740,6 +775,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -750,6 +786,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -761,6 +798,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -771,6 +809,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -782,6 +821,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -792,6 +832,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -803,6 +844,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -813,6 +855,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -824,6 +867,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -834,6 +878,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -852,6 +897,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>0403010</t>
@@ -861,6 +907,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -870,6 +917,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04</t>
@@ -921,6 +969,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04030301</t>
@@ -930,6 +979,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>-应用软件运维服务</t>
@@ -979,6 +1029,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>ERP\CRM\SCM\BIW</t>
@@ -988,6 +1039,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1052,6 +1104,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04030301</t>
@@ -1061,6 +1114,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04应用软件评估建议</t>
@@ -1072,6 +1126,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04030301</t>
@@ -1081,6 +1136,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04</t>
@@ -1118,13 +1174,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1132,18 +1195,21 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1151,12 +1217,14 @@
       <sz val="24"/>
       <color rgb="FFFF0000"/>
       <name val="黑体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1164,34 +1232,40 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="黑体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="黑体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="黑体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="黑体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1199,6 +1273,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1206,13 +1281,15 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="黑体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1221,6 +1298,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1229,6 +1307,7 @@
       <sz val="24"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1236,41 +1315,38 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="楷体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="楷体_GB2312"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1278,6 +1354,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1286,7 +1363,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1294,6 +1371,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1302,6 +1380,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1310,6 +1389,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1317,7 +1397,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1325,7 +1405,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1333,7 +1413,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1341,14 +1421,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1356,48 +1436,42 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1405,50 +1479,42 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="宋体"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="36">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1500,19 +1566,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1524,19 +1590,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1548,19 +1614,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1572,19 +1638,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1596,19 +1662,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1620,19 +1686,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1643,102 +1727,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1754,7 +1742,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1763,16 +1750,14 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1787,7 +1772,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1802,7 +1786,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -1817,7 +1800,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1826,7 +1808,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1837,427 +1818,617 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="56">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="75">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="35" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="25" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="10" xfId="25" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="56">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2 2 4" xfId="49"/>
-    <cellStyle name="常规 2 2 2" xfId="50"/>
-    <cellStyle name="常规 2 2 3" xfId="51"/>
-    <cellStyle name="常规 2 2" xfId="52"/>
-    <cellStyle name="常规 2" xfId="53"/>
-    <cellStyle name="常规 3" xfId="54"/>
-    <cellStyle name="常规 4" xfId="55"/>
+  <cellStyles count="61">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="千位分隔" xfId="20"/>
+    <cellStyle name="货币" xfId="21"/>
+    <cellStyle name="百分比" xfId="22"/>
+    <cellStyle name="千位分隔[0]" xfId="23"/>
+    <cellStyle name="货币[0]" xfId="24"/>
+    <cellStyle name="超链接" xfId="25"/>
+    <cellStyle name="已访问的超链接" xfId="26"/>
+    <cellStyle name="注释" xfId="27"/>
+    <cellStyle name="警告文本" xfId="28"/>
+    <cellStyle name="标题" xfId="29"/>
+    <cellStyle name="解释性文本" xfId="30"/>
+    <cellStyle name="标题 1" xfId="31"/>
+    <cellStyle name="标题 2" xfId="32"/>
+    <cellStyle name="标题 3" xfId="33"/>
+    <cellStyle name="标题 4" xfId="34"/>
+    <cellStyle name="输入" xfId="35"/>
+    <cellStyle name="输出" xfId="36"/>
+    <cellStyle name="计算" xfId="37"/>
+    <cellStyle name="检查单元格" xfId="38"/>
+    <cellStyle name="链接单元格" xfId="39"/>
+    <cellStyle name="汇总" xfId="40"/>
+    <cellStyle name="好" xfId="41"/>
+    <cellStyle name="差" xfId="42"/>
+    <cellStyle name="适中" xfId="43"/>
+    <cellStyle name="强调文字颜色 1" xfId="44"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="45"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="46"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="47"/>
+    <cellStyle name="强调文字颜色 2" xfId="48"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="49"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="50"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="51"/>
+    <cellStyle name="强调文字颜色 3" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="53"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="54"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="55"/>
+    <cellStyle name="强调文字颜色 4" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="57"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="58"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="59"/>
+    <cellStyle name="强调文字颜色 5" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="61"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="62"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="63"/>
+    <cellStyle name="强调文字颜色 6" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="65"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="66"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="67"/>
+    <cellStyle name="常规 2 2 4" xfId="68"/>
+    <cellStyle name="常规 2 2 2" xfId="69"/>
+    <cellStyle name="常规 2 2 3" xfId="70"/>
+    <cellStyle name="常规 2 2" xfId="71"/>
+    <cellStyle name="常规 2" xfId="72"/>
+    <cellStyle name="常规 3" xfId="73"/>
+    <cellStyle name="常规 4" xfId="74"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2552,23 +2723,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.11111111111111" customWidth="1"/>
-    <col min="2" max="2" width="7.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="9.88888888888889" customWidth="1"/>
-    <col min="4" max="4" width="12.8888888888889" customWidth="1"/>
-    <col min="5" max="5" width="14.1111111111111" customWidth="1"/>
-    <col min="6" max="6" width="17.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="6.125" customWidth="1"/>
+    <col min="2" max="2" width="7.625" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="12.7777777777778" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.1" customHeight="1"/>
-    <row r="3" spans="1:9">
+    <row r="1" spans="1:9" ht="14.1" customHeight="1"/>
+    <row r="2" spans="1:9" ht="14.4"/>
+    <row r="3" spans="1:9" ht="14.4">
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
@@ -2576,7 +2747,7 @@
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" ht="14.4">
       <c r="B4" s="49"/>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2584,7 +2755,7 @@
       <c r="F4" s="49"/>
       <c r="G4" s="49"/>
     </row>
-    <row r="5" ht="27" customHeight="1" spans="1:9">
+    <row r="5" spans="1:9" ht="27" customHeight="1">
       <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
@@ -2596,7 +2767,7 @@
       <c r="G5" s="50"/>
       <c r="H5" s="50"/>
     </row>
-    <row r="6" ht="48" customHeight="1" spans="1:9">
+    <row r="6" spans="1:9" ht="48" customHeight="1">
       <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
@@ -2608,7 +2779,7 @@
       <c r="G6" s="51"/>
       <c r="H6" s="51"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" ht="14.4">
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="49"/>
@@ -2621,7 +2792,7 @@
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" ht="14.4">
       <c r="B8" s="49"/>
       <c r="C8" s="49"/>
       <c r="D8" s="49"/>
@@ -2629,7 +2800,7 @@
       <c r="F8" s="49"/>
       <c r="G8" s="49"/>
     </row>
-    <row r="9" ht="21" customHeight="1" spans="1:9">
+    <row r="9" spans="1:9" ht="21" customHeight="1">
       <c r="A9" s="53" t="s">
         <v>4</v>
       </c>
@@ -2641,7 +2812,7 @@
       <c r="G9" s="53"/>
       <c r="H9" s="53"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" ht="14.4">
       <c r="A10" s="54" t="s">
         <v>5</v>
       </c>
@@ -2667,7 +2838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" ht="14.4">
       <c r="A11" s="56"/>
       <c r="B11" s="55"/>
       <c r="C11" s="57"/>
@@ -2680,7 +2851,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="35.1" customHeight="1" spans="1:9">
+    <row r="12" spans="1:9" ht="35.1" customHeight="1">
       <c r="A12" s="58">
         <v>1</v>
       </c>
@@ -2706,7 +2877,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" ht="30.9" customHeight="1" spans="1:9">
+    <row r="13" spans="1:8" ht="30.9" customHeight="1">
       <c r="A13" s="58"/>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
@@ -2716,7 +2887,7 @@
       <c r="G13" s="58"/>
       <c r="H13" s="58"/>
     </row>
-    <row r="14" ht="30.9" customHeight="1" spans="1:9">
+    <row r="14" spans="1:8" ht="30.9" customHeight="1">
       <c r="A14" s="58"/>
       <c r="B14" s="58"/>
       <c r="C14" s="58"/>
@@ -2726,7 +2897,7 @@
       <c r="G14" s="58"/>
       <c r="H14" s="58"/>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="1:9">
+    <row r="15" spans="1:8" ht="28" customHeight="1">
       <c r="A15" s="58"/>
       <c r="B15" s="58"/>
       <c r="C15" s="58"/>
@@ -2736,7 +2907,7 @@
       <c r="G15" s="58"/>
       <c r="H15" s="58"/>
     </row>
-    <row r="16" ht="33" customHeight="1" spans="1:9">
+    <row r="16" spans="1:8" ht="33" customHeight="1">
       <c r="A16" s="58"/>
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
@@ -2746,7 +2917,7 @@
       <c r="G16" s="58"/>
       <c r="H16" s="58"/>
     </row>
-    <row r="17" ht="27" customHeight="1" spans="1:8">
+    <row r="17" spans="1:8" ht="27" customHeight="1">
       <c r="A17" s="58"/>
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
@@ -2756,7 +2927,7 @@
       <c r="G17" s="58"/>
       <c r="H17" s="58"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="2:7" ht="14.4">
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -2764,7 +2935,7 @@
       <c r="F20" s="49"/>
       <c r="G20" s="49"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="2:7" ht="14.4">
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -2772,7 +2943,7 @@
       <c r="F21" s="49"/>
       <c r="G21" s="49"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="2:7" ht="14.4">
       <c r="B22" s="49"/>
       <c r="C22" s="49"/>
       <c r="D22" s="49"/>
@@ -2780,7 +2951,7 @@
       <c r="F22" s="49"/>
       <c r="G22" s="49"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="2:7" ht="14.4">
       <c r="B23" s="49"/>
       <c r="C23" s="49"/>
       <c r="D23" s="49"/>
@@ -2788,7 +2959,7 @@
       <c r="F23" s="49"/>
       <c r="G23" s="49"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="2:7" ht="14.4">
       <c r="B24" s="49"/>
       <c r="C24" s="49"/>
       <c r="D24" s="49"/>
@@ -2796,7 +2967,7 @@
       <c r="F24" s="49"/>
       <c r="G24" s="49"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="2:7" ht="14.4">
       <c r="B25" s="49"/>
       <c r="C25" s="49"/>
       <c r="D25" s="49"/>
@@ -2804,7 +2975,7 @@
       <c r="F25" s="49"/>
       <c r="G25" s="49"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="2:7" ht="14.4">
       <c r="B26" s="49"/>
       <c r="C26" s="49"/>
       <c r="D26" s="49"/>
@@ -2812,7 +2983,7 @@
       <c r="F26" s="49"/>
       <c r="G26" s="49"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="2:7" ht="14.4">
       <c r="B27" s="49"/>
       <c r="C27" s="49"/>
       <c r="D27" s="49"/>
@@ -2820,7 +2991,7 @@
       <c r="F27" s="49"/>
       <c r="G27" s="49"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="2:7" ht="14.4">
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
@@ -2843,29 +3014,27 @@
     <mergeCell ref="H10:H11"/>
   </mergeCells>
   <pageMargins left="0.0784722222222222" right="0.314583333333333" top="0.75" bottom="0.75" header="0.393055555555556" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="10.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="68.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4">
       <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" ht="17.25" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" ht="17.25" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -2873,7 +3042,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="17.25" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -2881,7 +3050,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="17.25" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -2889,7 +3058,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" spans="1:2">
+    <row r="5" spans="1:2" ht="17.25" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -2897,7 +3066,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="17.25" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -2905,7 +3074,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="17.25" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -2913,7 +3082,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="17.25" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
@@ -2921,7 +3090,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" ht="33" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="33" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
@@ -2929,7 +3098,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" ht="32.25" customHeight="1" spans="1:2">
+    <row r="10" spans="1:2" ht="32.25" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>79</v>
       </c>
@@ -2937,7 +3106,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" ht="19.5" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="19.5" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -2945,7 +3114,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" ht="144.75" customHeight="1" spans="1:2">
+    <row r="12" spans="1:2" ht="144.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
@@ -2953,7 +3122,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1" spans="1:2">
+    <row r="13" spans="1:2" ht="19.5" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>111</v>
       </c>
@@ -2961,7 +3130,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1" spans="1:2">
+    <row r="14" spans="1:2" ht="19.5" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -2969,7 +3138,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" ht="19.5" customHeight="1" spans="1:2">
+    <row r="15" spans="1:2" ht="19.5" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -2977,7 +3146,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="16" ht="19.5" customHeight="1" spans="1:2">
+    <row r="16" spans="1:2" ht="19.5" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -2990,30 +3159,28 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="5.44444444444444" style="23" customWidth="1"/>
-    <col min="3" max="3" width="7.22222222222222" style="23" customWidth="1"/>
-    <col min="4" max="4" width="7.44444444444444" style="23" customWidth="1"/>
-    <col min="5" max="5" width="9.88888888888889" style="23" customWidth="1"/>
+    <col min="1" max="2" width="5.5" style="23" customWidth="1"/>
+    <col min="3" max="3" width="7.25" style="23" customWidth="1"/>
+    <col min="4" max="4" width="7.5" style="23" customWidth="1"/>
+    <col min="5" max="5" width="9.875" style="23" customWidth="1"/>
     <col min="6" max="6" width="10" style="23" customWidth="1"/>
-    <col min="7" max="7" width="19.1111111111111" style="23" customWidth="1"/>
-    <col min="8" max="8" width="10.7777777777778" style="23" customWidth="1"/>
-    <col min="9" max="9" width="26.7777777777778" style="23" customWidth="1"/>
-    <col min="10" max="10" width="40.7777777777778" style="23" customWidth="1"/>
+    <col min="7" max="7" width="19.125" style="23" customWidth="1"/>
+    <col min="8" max="8" width="10.75" style="23" customWidth="1"/>
+    <col min="9" max="9" width="26.75" style="23" customWidth="1"/>
+    <col min="10" max="10" width="40.75" style="23" customWidth="1"/>
     <col min="11" max="16384" width="9" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35.25" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" ht="35.25" customHeight="1">
       <c r="A1" s="24" t="s">
         <v>19</v>
       </c>
@@ -3027,7 +3194,7 @@
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
     </row>
-    <row r="2" s="22" customFormat="1" ht="52.2" spans="1:10">
+    <row r="2" spans="1:10" s="22" customFormat="1" ht="52.2">
       <c r="A2" s="26" t="s">
         <v>20</v>
       </c>
@@ -3059,7 +3226,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" ht="14.4">
       <c r="A3" s="27" t="s">
         <v>30</v>
       </c>
@@ -3077,7 +3244,7 @@
       <c r="I3" s="33"/>
       <c r="J3" s="34"/>
     </row>
-    <row r="4" ht="28.8" spans="1:10">
+    <row r="4" spans="1:10" ht="28.8">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="35"/>
@@ -3093,7 +3260,7 @@
       <c r="I4" s="33"/>
       <c r="J4" s="34"/>
     </row>
-    <row r="5" ht="30" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="30" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="28"/>
       <c r="C5" s="35"/>
@@ -3109,7 +3276,7 @@
       <c r="I5" s="33"/>
       <c r="J5" s="34"/>
     </row>
-    <row r="6" ht="33" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="33" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="28"/>
       <c r="C6" s="35"/>
@@ -3127,7 +3294,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:10">
+    <row r="7" spans="1:10" ht="33" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="28"/>
       <c r="C7" s="35"/>
@@ -3145,7 +3312,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" spans="1:10">
+    <row r="8" spans="1:10" ht="33" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="28"/>
       <c r="C8" s="35"/>
@@ -3163,7 +3330,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" ht="33" customHeight="1" spans="1:10">
+    <row r="9" spans="1:10" ht="33" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="28"/>
       <c r="C9" s="35"/>
@@ -3181,7 +3348,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" ht="30.9" customHeight="1" spans="1:10">
+    <row r="10" spans="1:10" ht="30.9" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="28"/>
       <c r="C10" s="35"/>
@@ -3197,7 +3364,7 @@
       <c r="I10" s="33"/>
       <c r="J10" s="34"/>
     </row>
-    <row r="11" ht="33" customHeight="1" spans="1:10">
+    <row r="11" spans="1:10" ht="33" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="28"/>
       <c r="C11" s="35"/>
@@ -3213,7 +3380,7 @@
       <c r="I11" s="33"/>
       <c r="J11" s="34"/>
     </row>
-    <row r="12" ht="42" customHeight="1" spans="1:10">
+    <row r="12" spans="1:10" ht="42" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="28"/>
       <c r="C12" s="35"/>
@@ -3231,7 +3398,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" ht="32.1" customHeight="1" spans="1:10">
+    <row r="13" spans="1:10" ht="32.1" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="28"/>
       <c r="C13" s="35"/>
@@ -3249,7 +3416,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" ht="39" customHeight="1" spans="1:10">
+    <row r="14" spans="1:10" ht="39" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="28"/>
       <c r="C14" s="35"/>
@@ -3267,7 +3434,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" ht="33" customHeight="1" spans="1:10">
+    <row r="15" spans="1:10" ht="33" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="28"/>
       <c r="C15" s="48"/>
@@ -3299,30 +3466,28 @@
     <hyperlink ref="H15" location="'0403030101针对特种设备行业领域的应用软件巡检服务'!A1" display="0403030104"/>
   </hyperlinks>
   <pageMargins left="0.118055555555556" right="0.118055555555556" top="0.747916666666667" bottom="0.747916666666667" header="0.313888888888889" footer="0.313888888888889"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape" paperSize="9"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4">
       <c r="A1" s="18" t="s">
         <v>64</v>
       </c>
       <c r="B1" s="19"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.4">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3330,7 +3495,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="14.4">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3338,7 +3503,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="14.4">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3346,7 +3511,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="14.4">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3354,7 +3519,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="14.4">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3362,7 +3527,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="14.4">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -3370,7 +3535,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="14.4">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -3378,7 +3543,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:2">
+    <row r="9" spans="1:2" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -3386,13 +3551,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="14.4">
       <c r="A10" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="20"/>
     </row>
-    <row r="11" ht="21" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="21" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -3400,7 +3565,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" ht="288" spans="1:2">
+    <row r="12" spans="1:2" ht="288">
       <c r="A12" s="21" t="s">
         <v>82</v>
       </c>
@@ -3408,7 +3573,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:2">
+    <row r="13" spans="1:2" ht="28.8">
       <c r="A13" s="4" t="s">
         <v>84</v>
       </c>
@@ -3416,7 +3581,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14.4">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -3424,7 +3589,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="14.4">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -3432,7 +3597,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14.4">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -3446,29 +3611,27 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="13.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="59.4444444444444" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="13.625" customWidth="1"/>
+    <col min="2" max="2" width="59.5" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4">
       <c r="A1" s="18" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="19"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.4">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3476,7 +3639,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="14.4">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3484,7 +3647,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="14.4">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3492,7 +3655,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="14.4">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3500,7 +3663,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="14.4">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3508,7 +3671,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="14.4">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -3516,7 +3679,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="1:2">
+    <row r="8" spans="1:2" ht="28.8">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -3524,7 +3687,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:2">
+    <row r="9" spans="1:2" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -3532,13 +3695,13 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="14.4">
       <c r="A10" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="20"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="14.4">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -3546,7 +3709,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" ht="178.2" customHeight="1" spans="1:2">
+    <row r="12" spans="1:2" ht="178.2" customHeight="1">
       <c r="A12" s="21" t="s">
         <v>82</v>
       </c>
@@ -3554,7 +3717,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="14.4">
       <c r="A13" s="4" t="s">
         <v>84</v>
       </c>
@@ -3562,7 +3725,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14.4">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -3570,7 +3733,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="14.4">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -3578,7 +3741,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14.4">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -3592,29 +3755,27 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="54.1111111111111" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="54.125" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4">
       <c r="A1" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B1" s="19"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.4">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3622,7 +3783,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="14.4">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3630,7 +3791,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="14.4">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3638,7 +3799,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="14.4">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3646,7 +3807,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="14.4">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3654,7 +3815,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="14.4">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -3662,7 +3823,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="14.4">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -3670,7 +3831,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:2">
+    <row r="9" spans="1:2" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -3678,13 +3839,13 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="14.4">
       <c r="A10" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="20"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="14.4">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -3692,7 +3853,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" ht="230.4" spans="1:2">
+    <row r="12" spans="1:2" ht="230.4">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
@@ -3700,7 +3861,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="14.4">
       <c r="A13" s="4" t="s">
         <v>84</v>
       </c>
@@ -3708,7 +3869,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14.4">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -3716,7 +3877,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="14.4">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -3724,7 +3885,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14.4">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -3738,29 +3899,27 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="10.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="68.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="68.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:2">
+    <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>103</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" ht="24" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3768,7 +3927,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="24" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3776,7 +3935,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="24" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3784,7 +3943,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:2">
+    <row r="5" spans="1:2" ht="24" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3792,7 +3951,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="24" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3800,7 +3959,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="24" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -3808,7 +3967,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="24" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
@@ -3816,7 +3975,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" ht="42.75" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="42.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
@@ -3824,7 +3983,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" ht="40.5" customHeight="1" spans="1:2">
+    <row r="10" spans="1:2" ht="40.5" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>79</v>
       </c>
@@ -3832,7 +3991,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="24" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -3840,7 +3999,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" ht="120.75" customHeight="1" spans="1:2">
+    <row r="12" spans="1:2" ht="120.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
@@ -3848,7 +4007,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:2">
+    <row r="13" spans="1:2" ht="24" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>111</v>
       </c>
@@ -3856,7 +4015,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:2">
+    <row r="14" spans="1:2" ht="24" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -3864,7 +4023,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:2">
+    <row r="15" spans="1:2" ht="24" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -3872,7 +4031,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:2">
+    <row r="16" spans="1:2" ht="24" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -3885,29 +4044,27 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="21.2222222222222" customWidth="1"/>
-    <col min="2" max="2" width="57.4444444444444" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="21.25" customWidth="1"/>
+    <col min="2" max="2" width="57.5" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:2">
+    <row r="1" spans="1:2" ht="21" customHeight="1">
       <c r="A1" s="63" t="s">
         <v>115</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" ht="21" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3915,7 +4072,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="21" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3923,7 +4080,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="21" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3931,7 +4088,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:2">
+    <row r="5" spans="1:2" ht="21" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3939,7 +4096,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="21" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3947,7 +4104,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="21" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -3955,7 +4112,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="21" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -3963,7 +4120,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" ht="36.75" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="36.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -3971,13 +4128,13 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:2">
+    <row r="10" spans="1:2" ht="21" customHeight="1">
       <c r="A10" s="12" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="13"/>
     </row>
-    <row r="11" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="21" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -3985,7 +4142,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" ht="259.2" spans="1:2">
+    <row r="12" spans="1:2" ht="259.2">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
@@ -3993,7 +4150,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:2">
+    <row r="13" spans="1:2" ht="21" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>84</v>
       </c>
@@ -4001,7 +4158,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:2">
+    <row r="14" spans="1:2" ht="21" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -4009,7 +4166,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:2">
+    <row r="15" spans="1:2" ht="21" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -4017,7 +4174,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:2">
+    <row r="16" spans="1:2" ht="21" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -4031,29 +4188,27 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="21.2222222222222" customWidth="1"/>
-    <col min="2" max="2" width="62.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="21.25" customWidth="1"/>
+    <col min="2" max="2" width="62.25" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4">
       <c r="A1" s="63" t="s">
         <v>122</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" ht="24.75" customHeight="1" spans="1:2">
+    <row r="2" spans="1:2" ht="24.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -4061,7 +4216,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" ht="24.75" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="24.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -4069,7 +4224,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" ht="24.75" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="24.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -4077,7 +4232,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" ht="24.75" customHeight="1" spans="1:2">
+    <row r="5" spans="1:2" ht="24.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -4085,7 +4240,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" ht="24.75" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="24.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -4093,7 +4248,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" ht="24.75" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="24.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -4101,7 +4256,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" ht="24.75" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="24.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -4109,7 +4264,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" ht="33.75" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="33.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -4117,13 +4272,13 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="14.4">
       <c r="A10" s="12" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="13"/>
     </row>
-    <row r="11" ht="15.6" spans="1:2">
+    <row r="11" spans="1:2" ht="15.6">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -4131,7 +4286,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" ht="226.2" customHeight="1" spans="1:2">
+    <row r="12" spans="1:2" ht="226.2" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
@@ -4139,7 +4294,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="14.4">
       <c r="A13" s="4" t="s">
         <v>127</v>
       </c>
@@ -4147,7 +4302,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14.4">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -4155,7 +4310,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="14.4">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -4163,7 +4318,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14.4">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -4177,29 +4332,28 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A2:B17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="64.8888888888889" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="64.875" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4"/>
+    <row r="2" spans="1:2" ht="14.4">
       <c r="A2" s="10" t="s">
         <v>129</v>
       </c>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" ht="19.5" customHeight="1" spans="1:2">
+    <row r="3" spans="1:2" ht="19.5" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>65</v>
       </c>
@@ -4207,7 +4361,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" ht="19.5" customHeight="1" spans="1:2">
+    <row r="4" spans="1:2" ht="19.5" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
@@ -4215,7 +4369,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" ht="19.5" customHeight="1" spans="1:2">
+    <row r="5" spans="1:2" ht="19.5" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>69</v>
       </c>
@@ -4223,7 +4377,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" ht="19.5" customHeight="1" spans="1:2">
+    <row r="6" spans="1:2" ht="19.5" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>71</v>
       </c>
@@ -4231,7 +4385,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" ht="19.5" customHeight="1" spans="1:2">
+    <row r="7" spans="1:2" ht="19.5" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>73</v>
       </c>
@@ -4239,7 +4393,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" ht="19.5" customHeight="1" spans="1:2">
+    <row r="8" spans="1:2" ht="19.5" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -4247,7 +4401,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2" ht="19.5" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>105</v>
       </c>
@@ -4255,7 +4409,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:2">
+    <row r="10" spans="1:2" ht="28.8">
       <c r="A10" s="4" t="s">
         <v>106</v>
       </c>
@@ -4263,7 +4417,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:2">
+    <row r="11" spans="1:2" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>79</v>
       </c>
@@ -4271,7 +4425,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1" spans="1:2">
+    <row r="12" spans="1:2" ht="17.25" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>80</v>
       </c>
@@ -4279,7 +4433,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="13" ht="222.6" customHeight="1" spans="1:2">
+    <row r="13" spans="1:2" ht="222.6" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>82</v>
       </c>
@@ -4287,7 +4441,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1" spans="1:2">
+    <row r="14" spans="1:2" ht="17.25" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>111</v>
       </c>
@@ -4295,7 +4449,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1" spans="1:2">
+    <row r="15" spans="1:2" ht="17.25" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>86</v>
       </c>
@@ -4303,7 +4457,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1" spans="1:2">
+    <row r="16" spans="1:2" ht="17.25" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>88</v>
       </c>
@@ -4311,7 +4465,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1" spans="1:2">
+    <row r="17" spans="1:2" ht="17.25" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>90</v>
       </c>
@@ -4324,7 +4478,6 @@
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/1-运维服务目录/JXTX-01-02-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/JXTX-01-02-组织级运维服务目录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="23040" windowHeight="9060" tabRatio="751" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9575" tabRatio="751" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="修订页" sheetId="68" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="针对质监行业领域的应用软件优化改善服务">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">修订页!$A$5:$H$14</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +41,7 @@
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>微软用户</author>
@@ -54,7 +54,6 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t>微软用户:</t>
@@ -63,7 +62,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -76,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="143">
   <si>
     <t>江西通信产业服务有限公司</t>
   </si>
@@ -265,7 +263,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>040303010</t>
@@ -274,7 +271,6 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>4</t>
@@ -292,7 +288,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>040301010</t>
@@ -302,7 +297,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -312,7 +306,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>数据库系统巡检服务</t>
@@ -367,7 +360,7 @@
     <t>服务对象</t>
   </si>
   <si>
-    <t>主流的数据库管理软件：ORACLE</t>
+    <t>主流的数据库管理软件：MYSQL</t>
   </si>
   <si>
     <t>服务内容</t>
@@ -424,7 +417,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>040301010</t>
@@ -434,7 +426,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -444,7 +435,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>数据库系统故障处理服务</t>
@@ -489,7 +479,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -501,7 +490,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -512,7 +500,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -523,7 +510,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -535,7 +521,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -546,7 +531,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -558,7 +542,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -569,7 +552,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -581,7 +563,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -592,7 +573,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -604,7 +584,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -615,7 +594,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -627,7 +605,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -638,7 +615,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -649,7 +625,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -661,7 +636,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -672,7 +646,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -684,7 +657,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -695,7 +667,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -706,7 +677,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -717,7 +687,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -729,7 +698,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -740,7 +708,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -752,7 +719,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -763,7 +729,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -775,7 +740,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -786,7 +750,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -798,7 +761,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -809,7 +771,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -821,7 +782,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -832,7 +792,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -844,7 +803,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -855,7 +813,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -867,7 +824,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -878,7 +834,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -897,7 +852,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>0403010</t>
@@ -907,7 +861,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -917,7 +870,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04</t>
@@ -969,7 +921,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04030301</t>
@@ -979,7 +930,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>-应用软件运维服务</t>
@@ -992,7 +942,7 @@
     <t>确保管理系统运行正常，及时发现问题，保证机构能正常使用系统办理相关业务。</t>
   </si>
   <si>
-    <t>ERP\CRM\SCM\BIW等应用系统</t>
+    <t>ERP\CRM\等应用系统</t>
   </si>
   <si>
     <t>1、应用服务监控：
@@ -1029,7 +979,6 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>ERP\CRM\SCM\BIW</t>
@@ -1039,7 +988,6 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1074,6 +1022,9 @@
   </si>
   <si>
     <t>对SAP应用软件的功能、业务流程、性能等提供优化服务的技术支持</t>
+  </si>
+  <si>
+    <t>ERP\CRM\SCM\BIW等应用系统</t>
   </si>
   <si>
     <t>根据系统运行状况，提供系统优化技术支持，具体服务包括：
@@ -1104,7 +1055,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04030301</t>
@@ -1114,7 +1064,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04应用软件评估建议</t>
@@ -1126,7 +1075,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04030301</t>
@@ -1136,7 +1084,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>04</t>
@@ -1169,25 +1116,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1195,21 +1135,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1217,14 +1154,12 @@
       <sz val="24"/>
       <color rgb="FFFF0000"/>
       <name val="黑体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1232,40 +1167,34 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="黑体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="黑体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="黑体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="黑体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1273,7 +1202,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1281,15 +1209,13 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="黑体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u val="single"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1298,7 +1224,6 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1307,7 +1232,6 @@
       <sz val="24"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1315,38 +1239,34 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="楷体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="楷体_GB2312"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u val="single"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1354,7 +1274,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1363,7 +1282,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1371,7 +1290,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1380,7 +1298,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1389,7 +1306,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1397,7 +1313,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1405,7 +1321,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1413,7 +1329,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1421,14 +1337,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1436,85 +1352,97 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="36">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1702,24 +1630,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -1727,6 +1637,102 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1742,6 +1748,7 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1750,6 +1757,7 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1758,6 +1766,7 @@
       <bottom style="medium">
         <color theme="4" tint="0.49998"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1772,6 +1781,7 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1786,6 +1796,7 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -1800,6 +1811,7 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1808,6 +1820,7 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1818,617 +1831,345 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="75">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment/>
-    </xf>
+  <cellStyleXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
-    </xf>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="12" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="13" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="12" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="14" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-      <protection/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="60">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="68" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="34" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="35" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="25" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="10" xfId="25" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="61">
-    <cellStyle name="Normal" xfId="0"/>
-    <cellStyle name="Percent" xfId="15"/>
-    <cellStyle name="Currency" xfId="16"/>
-    <cellStyle name="Currency [0]" xfId="17"/>
-    <cellStyle name="Comma" xfId="18"/>
-    <cellStyle name="Comma [0]" xfId="19"/>
-    <cellStyle name="千位分隔" xfId="20"/>
-    <cellStyle name="货币" xfId="21"/>
-    <cellStyle name="百分比" xfId="22"/>
-    <cellStyle name="千位分隔[0]" xfId="23"/>
-    <cellStyle name="货币[0]" xfId="24"/>
-    <cellStyle name="超链接" xfId="25"/>
-    <cellStyle name="已访问的超链接" xfId="26"/>
-    <cellStyle name="注释" xfId="27"/>
-    <cellStyle name="警告文本" xfId="28"/>
-    <cellStyle name="标题" xfId="29"/>
-    <cellStyle name="解释性文本" xfId="30"/>
-    <cellStyle name="标题 1" xfId="31"/>
-    <cellStyle name="标题 2" xfId="32"/>
-    <cellStyle name="标题 3" xfId="33"/>
-    <cellStyle name="标题 4" xfId="34"/>
-    <cellStyle name="输入" xfId="35"/>
-    <cellStyle name="输出" xfId="36"/>
-    <cellStyle name="计算" xfId="37"/>
-    <cellStyle name="检查单元格" xfId="38"/>
-    <cellStyle name="链接单元格" xfId="39"/>
-    <cellStyle name="汇总" xfId="40"/>
-    <cellStyle name="好" xfId="41"/>
-    <cellStyle name="差" xfId="42"/>
-    <cellStyle name="适中" xfId="43"/>
-    <cellStyle name="强调文字颜色 1" xfId="44"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="45"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="46"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="47"/>
-    <cellStyle name="强调文字颜色 2" xfId="48"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="49"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="50"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="51"/>
-    <cellStyle name="强调文字颜色 3" xfId="52"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="53"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="54"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="55"/>
-    <cellStyle name="强调文字颜色 4" xfId="56"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="57"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="58"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="59"/>
-    <cellStyle name="强调文字颜色 5" xfId="60"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="61"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="62"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="63"/>
-    <cellStyle name="强调文字颜色 6" xfId="64"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="65"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="66"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="67"/>
-    <cellStyle name="常规 2 2 4" xfId="68"/>
-    <cellStyle name="常规 2 2 2" xfId="69"/>
-    <cellStyle name="常规 2 2 3" xfId="70"/>
-    <cellStyle name="常规 2 2" xfId="71"/>
-    <cellStyle name="常规 2" xfId="72"/>
-    <cellStyle name="常规 3" xfId="73"/>
-    <cellStyle name="常规 4" xfId="74"/>
+  <cellStyles count="62">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
+    <cellStyle name="Percent" xfId="50"/>
+    <cellStyle name="Currency" xfId="51"/>
+    <cellStyle name="Currency [0]" xfId="52"/>
+    <cellStyle name="Comma" xfId="53"/>
+    <cellStyle name="Comma [0]" xfId="54"/>
+    <cellStyle name="常规 2 2 4" xfId="55"/>
+    <cellStyle name="常规 2 2 2" xfId="56"/>
+    <cellStyle name="常规 2 2 3" xfId="57"/>
+    <cellStyle name="常规 2 2" xfId="58"/>
+    <cellStyle name="常规 2" xfId="59"/>
+    <cellStyle name="常规 3" xfId="60"/>
+    <cellStyle name="常规 4" xfId="61"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2723,23 +2464,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.125" customWidth="1"/>
-    <col min="2" max="2" width="7.625" customWidth="1"/>
-    <col min="3" max="3" width="9.875" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="1" max="1" width="6.12962962962963" customWidth="1"/>
+    <col min="2" max="2" width="7.62962962962963" customWidth="1"/>
+    <col min="3" max="3" width="9.87962962962963" customWidth="1"/>
+    <col min="4" max="4" width="12.8796296296296" customWidth="1"/>
+    <col min="5" max="5" width="14.1296296296296" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="12.75" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.1" customHeight="1"/>
-    <row r="2" spans="1:9" ht="14.4"/>
-    <row r="3" spans="1:9" ht="14.4">
+    <row r="1" ht="14.1" customHeight="1"/>
+    <row r="3" spans="1:9">
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
       <c r="D3" s="49"/>
@@ -2747,7 +2488,7 @@
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
     </row>
-    <row r="4" spans="1:9" ht="14.4">
+    <row r="4" spans="1:9">
       <c r="B4" s="49"/>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -2755,7 +2496,7 @@
       <c r="F4" s="49"/>
       <c r="G4" s="49"/>
     </row>
-    <row r="5" spans="1:9" ht="27" customHeight="1">
+    <row r="5" ht="27" customHeight="1" spans="1:9">
       <c r="A5" s="50" t="s">
         <v>0</v>
       </c>
@@ -2767,7 +2508,7 @@
       <c r="G5" s="50"/>
       <c r="H5" s="50"/>
     </row>
-    <row r="6" spans="1:9" ht="48" customHeight="1">
+    <row r="6" ht="48" customHeight="1" spans="1:9">
       <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
@@ -2779,7 +2520,7 @@
       <c r="G6" s="51"/>
       <c r="H6" s="51"/>
     </row>
-    <row r="7" spans="1:9" ht="14.4">
+    <row r="7" spans="1:9">
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="49"/>
@@ -2792,7 +2533,7 @@
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
     </row>
-    <row r="8" spans="1:9" ht="14.4">
+    <row r="8" spans="1:9">
       <c r="B8" s="49"/>
       <c r="C8" s="49"/>
       <c r="D8" s="49"/>
@@ -2800,7 +2541,7 @@
       <c r="F8" s="49"/>
       <c r="G8" s="49"/>
     </row>
-    <row r="9" spans="1:9" ht="21" customHeight="1">
+    <row r="9" ht="21" customHeight="1" spans="1:9">
       <c r="A9" s="53" t="s">
         <v>4</v>
       </c>
@@ -2812,7 +2553,7 @@
       <c r="G9" s="53"/>
       <c r="H9" s="53"/>
     </row>
-    <row r="10" spans="1:9" ht="14.4">
+    <row r="10" spans="1:9">
       <c r="A10" s="54" t="s">
         <v>5</v>
       </c>
@@ -2838,7 +2579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.4">
+    <row r="11" spans="1:9">
       <c r="A11" s="56"/>
       <c r="B11" s="55"/>
       <c r="C11" s="57"/>
@@ -2851,7 +2592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="35.1" customHeight="1">
+    <row r="12" ht="35.1" customHeight="1" spans="1:9">
       <c r="A12" s="58">
         <v>1</v>
       </c>
@@ -2877,7 +2618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30.9" customHeight="1">
+    <row r="13" ht="30.9" customHeight="1" spans="1:9">
       <c r="A13" s="58"/>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
@@ -2887,7 +2628,7 @@
       <c r="G13" s="58"/>
       <c r="H13" s="58"/>
     </row>
-    <row r="14" spans="1:8" ht="30.9" customHeight="1">
+    <row r="14" ht="30.9" customHeight="1" spans="1:9">
       <c r="A14" s="58"/>
       <c r="B14" s="58"/>
       <c r="C14" s="58"/>
@@ -2897,7 +2638,7 @@
       <c r="G14" s="58"/>
       <c r="H14" s="58"/>
     </row>
-    <row r="15" spans="1:8" ht="28" customHeight="1">
+    <row r="15" ht="28" customHeight="1" spans="1:9">
       <c r="A15" s="58"/>
       <c r="B15" s="58"/>
       <c r="C15" s="58"/>
@@ -2907,7 +2648,7 @@
       <c r="G15" s="58"/>
       <c r="H15" s="58"/>
     </row>
-    <row r="16" spans="1:8" ht="33" customHeight="1">
+    <row r="16" ht="33" customHeight="1" spans="1:9">
       <c r="A16" s="58"/>
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
@@ -2917,7 +2658,7 @@
       <c r="G16" s="58"/>
       <c r="H16" s="58"/>
     </row>
-    <row r="17" spans="1:8" ht="27" customHeight="1">
+    <row r="17" ht="27" customHeight="1" spans="1:8">
       <c r="A17" s="58"/>
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
@@ -2927,7 +2668,7 @@
       <c r="G17" s="58"/>
       <c r="H17" s="58"/>
     </row>
-    <row r="20" spans="2:7" ht="14.4">
+    <row r="20" spans="1:8">
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -2935,7 +2676,7 @@
       <c r="F20" s="49"/>
       <c r="G20" s="49"/>
     </row>
-    <row r="21" spans="2:7" ht="14.4">
+    <row r="21" spans="1:8">
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -2943,7 +2684,7 @@
       <c r="F21" s="49"/>
       <c r="G21" s="49"/>
     </row>
-    <row r="22" spans="2:7" ht="14.4">
+    <row r="22" spans="1:8">
       <c r="B22" s="49"/>
       <c r="C22" s="49"/>
       <c r="D22" s="49"/>
@@ -2951,7 +2692,7 @@
       <c r="F22" s="49"/>
       <c r="G22" s="49"/>
     </row>
-    <row r="23" spans="2:7" ht="14.4">
+    <row r="23" spans="1:8">
       <c r="B23" s="49"/>
       <c r="C23" s="49"/>
       <c r="D23" s="49"/>
@@ -2959,7 +2700,7 @@
       <c r="F23" s="49"/>
       <c r="G23" s="49"/>
     </row>
-    <row r="24" spans="2:7" ht="14.4">
+    <row r="24" spans="1:8">
       <c r="B24" s="49"/>
       <c r="C24" s="49"/>
       <c r="D24" s="49"/>
@@ -2967,7 +2708,7 @@
       <c r="F24" s="49"/>
       <c r="G24" s="49"/>
     </row>
-    <row r="25" spans="2:7" ht="14.4">
+    <row r="25" spans="1:8">
       <c r="B25" s="49"/>
       <c r="C25" s="49"/>
       <c r="D25" s="49"/>
@@ -2975,7 +2716,7 @@
       <c r="F25" s="49"/>
       <c r="G25" s="49"/>
     </row>
-    <row r="26" spans="2:7" ht="14.4">
+    <row r="26" spans="1:8">
       <c r="B26" s="49"/>
       <c r="C26" s="49"/>
       <c r="D26" s="49"/>
@@ -2983,7 +2724,7 @@
       <c r="F26" s="49"/>
       <c r="G26" s="49"/>
     </row>
-    <row r="27" spans="2:7" ht="14.4">
+    <row r="27" spans="1:8">
       <c r="B27" s="49"/>
       <c r="C27" s="49"/>
       <c r="D27" s="49"/>
@@ -2991,7 +2732,7 @@
       <c r="F27" s="49"/>
       <c r="G27" s="49"/>
     </row>
-    <row r="28" spans="2:7" ht="14.4">
+    <row r="28" spans="1:8">
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49"/>
@@ -3014,27 +2755,29 @@
     <mergeCell ref="H10:H11"/>
   </mergeCells>
   <pageMargins left="0.0784722222222222" right="0.314583333333333" top="0.75" bottom="0.75" header="0.393055555555556" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="10.8796296296296" customWidth="1"/>
     <col min="2" max="2" width="68.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3042,7 +2785,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3050,7 +2793,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3058,7 +2801,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3066,15 +2809,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="17.25" customHeight="1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -3082,7 +2825,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
@@ -3090,39 +2833,39 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="33" customHeight="1">
+    <row r="9" ht="33" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="32.25" customHeight="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" ht="32.25" customHeight="1" spans="1:2">
       <c r="A10" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="19.5" customHeight="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" ht="19.5" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="144.75" customHeight="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" ht="144.75" customHeight="1" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="19.5" customHeight="1">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>111</v>
       </c>
@@ -3130,7 +2873,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="19.5" customHeight="1">
+    <row r="14" ht="19.5" customHeight="1" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -3138,20 +2881,20 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="19.5" customHeight="1">
+    <row r="15" ht="19.5" customHeight="1" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="19.5" customHeight="1">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3159,28 +2902,30 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="5.5" style="23" customWidth="1"/>
     <col min="3" max="3" width="7.25" style="23" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="23" customWidth="1"/>
-    <col min="5" max="5" width="9.875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="9.87962962962963" style="23" customWidth="1"/>
     <col min="6" max="6" width="10" style="23" customWidth="1"/>
-    <col min="7" max="7" width="19.125" style="23" customWidth="1"/>
+    <col min="7" max="7" width="19.1296296296296" style="23" customWidth="1"/>
     <col min="8" max="8" width="10.75" style="23" customWidth="1"/>
     <col min="9" max="9" width="26.75" style="23" customWidth="1"/>
     <col min="10" max="10" width="40.75" style="23" customWidth="1"/>
     <col min="11" max="16384" width="9" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="35.25" customHeight="1">
+    <row r="1" ht="35.25" customHeight="1" spans="1:10">
       <c r="A1" s="24" t="s">
         <v>19</v>
       </c>
@@ -3194,7 +2939,7 @@
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
     </row>
-    <row r="2" spans="1:10" s="22" customFormat="1" ht="52.2">
+    <row r="2" s="22" customFormat="1" ht="52.2" spans="1:10">
       <c r="A2" s="26" t="s">
         <v>20</v>
       </c>
@@ -3226,7 +2971,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.4">
+    <row r="3" spans="1:10">
       <c r="A3" s="27" t="s">
         <v>30</v>
       </c>
@@ -3244,7 +2989,7 @@
       <c r="I3" s="33"/>
       <c r="J3" s="34"/>
     </row>
-    <row r="4" spans="1:10" ht="28.8">
+    <row r="4" ht="28.8" spans="1:10">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="35"/>
@@ -3260,7 +3005,7 @@
       <c r="I4" s="33"/>
       <c r="J4" s="34"/>
     </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1">
+    <row r="5" ht="30" customHeight="1" spans="1:10">
       <c r="A5" s="27"/>
       <c r="B5" s="28"/>
       <c r="C5" s="35"/>
@@ -3276,7 +3021,7 @@
       <c r="I5" s="33"/>
       <c r="J5" s="34"/>
     </row>
-    <row r="6" spans="1:10" ht="33" customHeight="1">
+    <row r="6" ht="33" customHeight="1" spans="1:10">
       <c r="A6" s="27"/>
       <c r="B6" s="28"/>
       <c r="C6" s="35"/>
@@ -3294,7 +3039,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="33" customHeight="1">
+    <row r="7" ht="33" customHeight="1" spans="1:10">
       <c r="A7" s="27"/>
       <c r="B7" s="28"/>
       <c r="C7" s="35"/>
@@ -3312,7 +3057,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="33" customHeight="1">
+    <row r="8" ht="33" customHeight="1" spans="1:10">
       <c r="A8" s="27"/>
       <c r="B8" s="28"/>
       <c r="C8" s="35"/>
@@ -3330,7 +3075,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="33" customHeight="1">
+    <row r="9" ht="33" customHeight="1" spans="1:10">
       <c r="A9" s="27"/>
       <c r="B9" s="28"/>
       <c r="C9" s="35"/>
@@ -3348,7 +3093,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30.9" customHeight="1">
+    <row r="10" ht="30.9" customHeight="1" spans="1:10">
       <c r="A10" s="27"/>
       <c r="B10" s="28"/>
       <c r="C10" s="35"/>
@@ -3364,7 +3109,7 @@
       <c r="I10" s="33"/>
       <c r="J10" s="34"/>
     </row>
-    <row r="11" spans="1:10" ht="33" customHeight="1">
+    <row r="11" ht="33" customHeight="1" spans="1:10">
       <c r="A11" s="27"/>
       <c r="B11" s="28"/>
       <c r="C11" s="35"/>
@@ -3380,7 +3125,7 @@
       <c r="I11" s="33"/>
       <c r="J11" s="34"/>
     </row>
-    <row r="12" spans="1:10" ht="42" customHeight="1">
+    <row r="12" ht="42" customHeight="1" spans="1:10">
       <c r="A12" s="27"/>
       <c r="B12" s="28"/>
       <c r="C12" s="35"/>
@@ -3398,7 +3143,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="32.1" customHeight="1">
+    <row r="13" ht="32.1" customHeight="1" spans="1:10">
       <c r="A13" s="27"/>
       <c r="B13" s="28"/>
       <c r="C13" s="35"/>
@@ -3416,7 +3161,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="39" customHeight="1">
+    <row r="14" ht="39" customHeight="1" spans="1:10">
       <c r="A14" s="27"/>
       <c r="B14" s="28"/>
       <c r="C14" s="35"/>
@@ -3434,7 +3179,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="33" customHeight="1">
+    <row r="15" ht="33" customHeight="1" spans="1:10">
       <c r="A15" s="27"/>
       <c r="B15" s="28"/>
       <c r="C15" s="48"/>
@@ -3466,28 +3211,30 @@
     <hyperlink ref="H15" location="'0403030101针对特种设备行业领域的应用软件巡检服务'!A1" display="0403030104"/>
   </hyperlinks>
   <pageMargins left="0.118055555555556" right="0.118055555555556" top="0.747916666666667" bottom="0.747916666666667" header="0.313888888888889" footer="0.313888888888889"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="18" t="s">
         <v>64</v>
       </c>
       <c r="B1" s="19"/>
     </row>
-    <row r="2" spans="1:2" ht="14.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3495,7 +3242,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3503,7 +3250,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.4">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3511,7 +3258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.4">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3519,7 +3266,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.4">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3527,7 +3274,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.4">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -3535,7 +3282,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.4">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -3543,7 +3290,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="28.8">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -3551,13 +3298,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.4">
+    <row r="10" spans="1:2">
       <c r="A10" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="20"/>
     </row>
-    <row r="11" spans="1:2" ht="21" customHeight="1">
+    <row r="11" ht="21" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -3565,7 +3312,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="288">
+    <row r="12" ht="288" spans="1:2">
       <c r="A12" s="21" t="s">
         <v>82</v>
       </c>
@@ -3573,7 +3320,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="28.8">
+    <row r="13" ht="28.8" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>84</v>
       </c>
@@ -3581,7 +3328,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.4">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -3589,7 +3336,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.4">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -3597,7 +3344,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.4">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -3611,27 +3358,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="13.6296296296296" customWidth="1"/>
     <col min="2" max="2" width="59.5" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="18" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="19"/>
     </row>
-    <row r="2" spans="1:2" ht="14.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3639,7 +3388,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3647,7 +3396,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.4">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3655,7 +3404,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.4">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3663,7 +3412,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.4">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3671,7 +3420,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.4">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -3679,7 +3428,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="28.8">
+    <row r="8" ht="28.8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -3687,7 +3436,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="28.8">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -3695,13 +3444,13 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.4">
+    <row r="10" spans="1:2">
       <c r="A10" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="20"/>
     </row>
-    <row r="11" spans="1:2" ht="14.4">
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -3709,7 +3458,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="178.2" customHeight="1">
+    <row r="12" ht="178.2" customHeight="1" spans="1:2">
       <c r="A12" s="21" t="s">
         <v>82</v>
       </c>
@@ -3717,7 +3466,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.4">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>84</v>
       </c>
@@ -3725,7 +3474,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.4">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -3733,7 +3482,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.4">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -3741,7 +3490,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.4">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -3755,27 +3504,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="15.625" customWidth="1"/>
-    <col min="2" max="2" width="54.125" customWidth="1"/>
+    <col min="1" max="1" width="15.6296296296296" customWidth="1"/>
+    <col min="2" max="2" width="54.1296296296296" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B1" s="19"/>
     </row>
-    <row r="2" spans="1:2" ht="14.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3783,7 +3534,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3791,7 +3542,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.4">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3799,7 +3550,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.4">
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3807,7 +3558,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.4">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3815,7 +3566,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.4">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -3823,7 +3574,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.4">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -3831,7 +3582,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="28.8">
+    <row r="9" ht="28.8" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -3839,13 +3590,13 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.4">
+    <row r="10" spans="1:2">
       <c r="A10" s="20" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="20"/>
     </row>
-    <row r="11" spans="1:2" ht="14.4">
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -3853,7 +3604,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="230.4">
+    <row r="12" ht="230.4" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
@@ -3861,7 +3612,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.4">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>84</v>
       </c>
@@ -3869,7 +3620,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.4">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -3877,7 +3628,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.4">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -3885,7 +3636,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.4">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -3899,27 +3650,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="10.8796296296296" customWidth="1"/>
     <col min="2" max="2" width="68.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1">
+    <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="10" t="s">
         <v>103</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" ht="24" customHeight="1">
+    <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -3927,7 +3680,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="24" customHeight="1">
+    <row r="3" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -3935,7 +3688,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24" customHeight="1">
+    <row r="4" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -3943,7 +3696,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="24" customHeight="1">
+    <row r="5" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -3951,7 +3704,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="24" customHeight="1">
+    <row r="6" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -3959,7 +3712,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="24" customHeight="1">
+    <row r="7" customHeight="1" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -3967,7 +3720,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="24" customHeight="1">
+    <row r="8" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
@@ -3975,7 +3728,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="42.75" customHeight="1">
+    <row r="9" ht="42.75" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
@@ -3983,7 +3736,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="40.5" customHeight="1">
+    <row r="10" ht="40.5" customHeight="1" spans="1:2">
       <c r="A10" s="4" t="s">
         <v>79</v>
       </c>
@@ -3991,7 +3744,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="24" customHeight="1">
+    <row r="11" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -3999,7 +3752,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="120.75" customHeight="1">
+    <row r="12" ht="120.75" customHeight="1" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
@@ -4007,7 +3760,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="24" customHeight="1">
+    <row r="13" customHeight="1" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>111</v>
       </c>
@@ -4015,7 +3768,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24" customHeight="1">
+    <row r="14" customHeight="1" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -4023,7 +3776,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24" customHeight="1">
+    <row r="15" customHeight="1" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -4031,7 +3784,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="24" customHeight="1">
+    <row r="16" customHeight="1" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -4044,27 +3797,29 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
-    <col min="2" max="2" width="57.5" customWidth="1"/>
+    <col min="2" max="2" width="60.7777777777778" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" customHeight="1">
+    <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="63" t="s">
         <v>115</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" ht="21" customHeight="1">
+    <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -4072,7 +3827,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="21" customHeight="1">
+    <row r="3" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -4080,7 +3835,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="21" customHeight="1">
+    <row r="4" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -4088,7 +3843,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="21" customHeight="1">
+    <row r="5" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -4096,7 +3851,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="21" customHeight="1">
+    <row r="6" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -4104,7 +3859,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="21" customHeight="1">
+    <row r="7" customHeight="1" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -4112,7 +3867,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="21" customHeight="1">
+    <row r="8" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -4120,7 +3875,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="36.75" customHeight="1">
+    <row r="9" ht="36.75" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -4128,13 +3883,13 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="21" customHeight="1">
+    <row r="10" customHeight="1" spans="1:2">
       <c r="A10" s="12" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="13"/>
     </row>
-    <row r="11" spans="1:2" ht="21" customHeight="1">
+    <row r="11" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -4142,7 +3897,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="259.2">
+    <row r="12" ht="259.2" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
@@ -4150,7 +3905,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="21" customHeight="1">
+    <row r="13" customHeight="1" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>84</v>
       </c>
@@ -4158,7 +3913,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="21" customHeight="1">
+    <row r="14" customHeight="1" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -4166,7 +3921,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="21" customHeight="1">
+    <row r="15" customHeight="1" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -4174,7 +3929,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="21" customHeight="1">
+    <row r="16" customHeight="1" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -4188,27 +3943,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="21.25" customWidth="1"/>
     <col min="2" max="2" width="62.25" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="63" t="s">
         <v>122</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" ht="24.75" customHeight="1">
+    <row r="2" ht="24.75" customHeight="1" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -4216,7 +3973,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="24.75" customHeight="1">
+    <row r="3" ht="24.75" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
@@ -4224,7 +3981,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.75" customHeight="1">
+    <row r="4" ht="24.75" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -4232,7 +3989,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="24.75" customHeight="1">
+    <row r="5" ht="24.75" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>71</v>
       </c>
@@ -4240,7 +3997,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="24.75" customHeight="1">
+    <row r="6" ht="24.75" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -4248,7 +4005,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="24.75" customHeight="1">
+    <row r="7" ht="24.75" customHeight="1" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>74</v>
       </c>
@@ -4256,7 +4013,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="24.75" customHeight="1">
+    <row r="8" ht="24.75" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>75</v>
       </c>
@@ -4264,7 +4021,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="33.75" customHeight="1">
+    <row r="9" ht="33.75" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>77</v>
       </c>
@@ -4272,13 +4029,13 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.4">
+    <row r="10" spans="1:2">
       <c r="A10" s="12" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="13"/>
     </row>
-    <row r="11" spans="1:2" ht="15.6">
+    <row r="11" ht="15.6" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>80</v>
       </c>
@@ -4286,7 +4043,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="226.2" customHeight="1">
+    <row r="12" ht="226.2" customHeight="1" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>82</v>
       </c>
@@ -4294,7 +4051,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.4">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>127</v>
       </c>
@@ -4302,7 +4059,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.4">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>86</v>
       </c>
@@ -4310,7 +4067,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.4">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>88</v>
       </c>
@@ -4318,7 +4075,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.4">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>90</v>
       </c>
@@ -4332,28 +4089,29 @@
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetPr/>
+  <dimension ref="A2:B17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="64.875" customWidth="1"/>
+    <col min="2" max="2" width="64.8796296296296" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.4"/>
-    <row r="2" spans="1:2" ht="14.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="10" t="s">
         <v>129</v>
       </c>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" ht="19.5" customHeight="1">
+    <row r="3" ht="19.5" customHeight="1" spans="1:2">
       <c r="A3" s="4" t="s">
         <v>65</v>
       </c>
@@ -4361,7 +4119,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="19.5" customHeight="1">
+    <row r="4" ht="19.5" customHeight="1" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>67</v>
       </c>
@@ -4369,7 +4127,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="19.5" customHeight="1">
+    <row r="5" ht="19.5" customHeight="1" spans="1:2">
       <c r="A5" s="4" t="s">
         <v>69</v>
       </c>
@@ -4377,7 +4135,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="19.5" customHeight="1">
+    <row r="6" ht="19.5" customHeight="1" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>71</v>
       </c>
@@ -4385,7 +4143,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="19.5" customHeight="1">
+    <row r="7" ht="19.5" customHeight="1" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>73</v>
       </c>
@@ -4393,7 +4151,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="19.5" customHeight="1">
+    <row r="8" ht="19.5" customHeight="1" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -4401,7 +4159,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="19.5" customHeight="1">
+    <row r="9" ht="19.5" customHeight="1" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>105</v>
       </c>
@@ -4409,7 +4167,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.8">
+    <row r="10" ht="28.8" spans="1:2">
       <c r="A10" s="4" t="s">
         <v>106</v>
       </c>
@@ -4417,7 +4175,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" customHeight="1">
+    <row r="11" ht="15.75" customHeight="1" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>79</v>
       </c>
@@ -4425,23 +4183,23 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="222.6" customHeight="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" ht="222.6" customHeight="1" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="17.25" customHeight="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" ht="17.25" customHeight="1" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>111</v>
       </c>
@@ -4449,7 +4207,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>86</v>
       </c>
@@ -4457,20 +4215,20 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="17.25" customHeight="1">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" ht="17.25" customHeight="1" spans="1:2">
       <c r="A17" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -4478,6 +4236,7 @@
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>